--- a/Middleput/points.xlsx
+++ b/Middleput/points.xlsx
@@ -429,7 +429,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AF422"/>
+  <dimension ref="A1:AF440"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -46902,6 +46902,1986 @@
       </c>
       <c r="AF422" t="n">
         <v>11</v>
+      </c>
+    </row>
+    <row r="423">
+      <c r="A423" s="2" t="n">
+        <v>45170</v>
+      </c>
+      <c r="B423" t="n">
+        <v>2</v>
+      </c>
+      <c r="C423" t="n">
+        <v>1</v>
+      </c>
+      <c r="D423" t="inlineStr">
+        <is>
+          <t>5-a-side</t>
+        </is>
+      </c>
+      <c r="E423" t="inlineStr">
+        <is>
+          <t>Wissam Rahal</t>
+        </is>
+      </c>
+      <c r="F423" t="inlineStr">
+        <is>
+          <t>Offensive</t>
+        </is>
+      </c>
+      <c r="G423" t="inlineStr">
+        <is>
+          <t>Team A</t>
+        </is>
+      </c>
+      <c r="H423" t="inlineStr">
+        <is>
+          <t>Team A</t>
+        </is>
+      </c>
+      <c r="I423" t="inlineStr">
+        <is>
+          <t>Win</t>
+        </is>
+      </c>
+      <c r="J423" t="n">
+        <v>9</v>
+      </c>
+      <c r="K423" t="n">
+        <v>0</v>
+      </c>
+      <c r="L423" t="n">
+        <v>0</v>
+      </c>
+      <c r="M423" t="n">
+        <v>0</v>
+      </c>
+      <c r="N423" t="n">
+        <v>0</v>
+      </c>
+      <c r="O423" t="n">
+        <v>0</v>
+      </c>
+      <c r="P423" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q423" t="n">
+        <v>10</v>
+      </c>
+      <c r="R423" t="n">
+        <v>5</v>
+      </c>
+      <c r="S423" t="n">
+        <v>5</v>
+      </c>
+      <c r="T423" t="n">
+        <v>5</v>
+      </c>
+      <c r="U423" t="n">
+        <v>4</v>
+      </c>
+      <c r="V423" t="n">
+        <v>3</v>
+      </c>
+      <c r="W423" t="n">
+        <v>0</v>
+      </c>
+      <c r="X423" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y423" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z423" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA423" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB423" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC423" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD423" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE423" t="n">
+        <v>5</v>
+      </c>
+      <c r="AF423" t="n">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="424">
+      <c r="A424" s="2" t="n">
+        <v>45170</v>
+      </c>
+      <c r="B424" t="n">
+        <v>2</v>
+      </c>
+      <c r="C424" t="n">
+        <v>1</v>
+      </c>
+      <c r="D424" t="inlineStr">
+        <is>
+          <t>5-a-side</t>
+        </is>
+      </c>
+      <c r="E424" t="inlineStr">
+        <is>
+          <t>Cameron McAinsh</t>
+        </is>
+      </c>
+      <c r="F424" t="inlineStr">
+        <is>
+          <t>Outfield</t>
+        </is>
+      </c>
+      <c r="G424" t="inlineStr">
+        <is>
+          <t>Team A</t>
+        </is>
+      </c>
+      <c r="H424" t="inlineStr">
+        <is>
+          <t>Team A</t>
+        </is>
+      </c>
+      <c r="I424" t="inlineStr">
+        <is>
+          <t>Win</t>
+        </is>
+      </c>
+      <c r="J424" t="n">
+        <v>9</v>
+      </c>
+      <c r="K424" t="n">
+        <v>3</v>
+      </c>
+      <c r="L424" t="n">
+        <v>0</v>
+      </c>
+      <c r="M424" t="n">
+        <v>0</v>
+      </c>
+      <c r="N424" t="n">
+        <v>0</v>
+      </c>
+      <c r="O424" t="n">
+        <v>0</v>
+      </c>
+      <c r="P424" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q424" t="n">
+        <v>10</v>
+      </c>
+      <c r="R424" t="n">
+        <v>5</v>
+      </c>
+      <c r="S424" t="n">
+        <v>5</v>
+      </c>
+      <c r="T424" t="n">
+        <v>5</v>
+      </c>
+      <c r="U424" t="n">
+        <v>4</v>
+      </c>
+      <c r="V424" t="n">
+        <v>3</v>
+      </c>
+      <c r="W424" t="n">
+        <v>0</v>
+      </c>
+      <c r="X424" t="n">
+        <v>3</v>
+      </c>
+      <c r="Y424" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z424" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA424" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB424" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC424" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD424" t="n">
+        <v>3</v>
+      </c>
+      <c r="AE424" t="n">
+        <v>5</v>
+      </c>
+      <c r="AF424" t="n">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="425">
+      <c r="A425" s="2" t="n">
+        <v>45170</v>
+      </c>
+      <c r="B425" t="n">
+        <v>2</v>
+      </c>
+      <c r="C425" t="n">
+        <v>1</v>
+      </c>
+      <c r="D425" t="inlineStr">
+        <is>
+          <t>5-a-side</t>
+        </is>
+      </c>
+      <c r="E425" t="inlineStr">
+        <is>
+          <t>Damiano Barbanera</t>
+        </is>
+      </c>
+      <c r="F425" t="inlineStr">
+        <is>
+          <t>Outfield</t>
+        </is>
+      </c>
+      <c r="G425" t="inlineStr">
+        <is>
+          <t>Team A</t>
+        </is>
+      </c>
+      <c r="H425" t="inlineStr">
+        <is>
+          <t>Team A</t>
+        </is>
+      </c>
+      <c r="I425" t="inlineStr">
+        <is>
+          <t>Win</t>
+        </is>
+      </c>
+      <c r="J425" t="n">
+        <v>9</v>
+      </c>
+      <c r="K425" t="n">
+        <v>1</v>
+      </c>
+      <c r="L425" t="n">
+        <v>0</v>
+      </c>
+      <c r="M425" t="n">
+        <v>0</v>
+      </c>
+      <c r="N425" t="n">
+        <v>0</v>
+      </c>
+      <c r="O425" t="n">
+        <v>0</v>
+      </c>
+      <c r="P425" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q425" t="n">
+        <v>10</v>
+      </c>
+      <c r="R425" t="n">
+        <v>5</v>
+      </c>
+      <c r="S425" t="n">
+        <v>5</v>
+      </c>
+      <c r="T425" t="n">
+        <v>5</v>
+      </c>
+      <c r="U425" t="n">
+        <v>4</v>
+      </c>
+      <c r="V425" t="n">
+        <v>3</v>
+      </c>
+      <c r="W425" t="n">
+        <v>0</v>
+      </c>
+      <c r="X425" t="n">
+        <v>1</v>
+      </c>
+      <c r="Y425" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z425" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA425" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB425" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC425" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD425" t="n">
+        <v>3</v>
+      </c>
+      <c r="AE425" t="n">
+        <v>5</v>
+      </c>
+      <c r="AF425" t="n">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="426">
+      <c r="A426" s="2" t="n">
+        <v>45170</v>
+      </c>
+      <c r="B426" t="n">
+        <v>2</v>
+      </c>
+      <c r="C426" t="n">
+        <v>1</v>
+      </c>
+      <c r="D426" t="inlineStr">
+        <is>
+          <t>5-a-side</t>
+        </is>
+      </c>
+      <c r="E426" t="inlineStr">
+        <is>
+          <t>Ludovico Righi</t>
+        </is>
+      </c>
+      <c r="F426" t="inlineStr">
+        <is>
+          <t>Outfield</t>
+        </is>
+      </c>
+      <c r="G426" t="inlineStr">
+        <is>
+          <t>Team A</t>
+        </is>
+      </c>
+      <c r="H426" t="inlineStr">
+        <is>
+          <t>Team A</t>
+        </is>
+      </c>
+      <c r="I426" t="inlineStr">
+        <is>
+          <t>Win</t>
+        </is>
+      </c>
+      <c r="J426" t="n">
+        <v>9</v>
+      </c>
+      <c r="K426" t="n">
+        <v>0</v>
+      </c>
+      <c r="L426" t="n">
+        <v>0</v>
+      </c>
+      <c r="M426" t="n">
+        <v>0</v>
+      </c>
+      <c r="N426" t="n">
+        <v>0</v>
+      </c>
+      <c r="O426" t="n">
+        <v>0</v>
+      </c>
+      <c r="P426" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q426" t="n">
+        <v>10</v>
+      </c>
+      <c r="R426" t="n">
+        <v>5</v>
+      </c>
+      <c r="S426" t="n">
+        <v>5</v>
+      </c>
+      <c r="T426" t="n">
+        <v>5</v>
+      </c>
+      <c r="U426" t="n">
+        <v>4</v>
+      </c>
+      <c r="V426" t="n">
+        <v>3</v>
+      </c>
+      <c r="W426" t="n">
+        <v>0</v>
+      </c>
+      <c r="X426" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y426" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z426" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA426" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB426" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC426" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD426" t="n">
+        <v>3</v>
+      </c>
+      <c r="AE426" t="n">
+        <v>5</v>
+      </c>
+      <c r="AF426" t="n">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="427">
+      <c r="A427" s="2" t="n">
+        <v>45170</v>
+      </c>
+      <c r="B427" t="n">
+        <v>2</v>
+      </c>
+      <c r="C427" t="n">
+        <v>1</v>
+      </c>
+      <c r="D427" t="inlineStr">
+        <is>
+          <t>5-a-side</t>
+        </is>
+      </c>
+      <c r="E427" t="inlineStr">
+        <is>
+          <t>Federico Paolucci</t>
+        </is>
+      </c>
+      <c r="F427" t="inlineStr">
+        <is>
+          <t>Outfield</t>
+        </is>
+      </c>
+      <c r="G427" t="inlineStr">
+        <is>
+          <t>Team B</t>
+        </is>
+      </c>
+      <c r="H427" t="inlineStr">
+        <is>
+          <t>Team A</t>
+        </is>
+      </c>
+      <c r="I427" t="inlineStr">
+        <is>
+          <t>Loss</t>
+        </is>
+      </c>
+      <c r="J427" t="n">
+        <v>9</v>
+      </c>
+      <c r="K427" t="n">
+        <v>0</v>
+      </c>
+      <c r="L427" t="n">
+        <v>0</v>
+      </c>
+      <c r="M427" t="n">
+        <v>0</v>
+      </c>
+      <c r="N427" t="n">
+        <v>0</v>
+      </c>
+      <c r="O427" t="n">
+        <v>0</v>
+      </c>
+      <c r="P427" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q427" t="n">
+        <v>10</v>
+      </c>
+      <c r="R427" t="n">
+        <v>5</v>
+      </c>
+      <c r="S427" t="n">
+        <v>10</v>
+      </c>
+      <c r="T427" t="n">
+        <v>-5</v>
+      </c>
+      <c r="U427" t="n">
+        <v>4</v>
+      </c>
+      <c r="V427" t="n">
+        <v>0</v>
+      </c>
+      <c r="W427" t="n">
+        <v>0</v>
+      </c>
+      <c r="X427" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y427" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z427" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA427" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB427" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC427" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD427" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE427" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF427" t="n">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="428">
+      <c r="A428" s="2" t="n">
+        <v>45170</v>
+      </c>
+      <c r="B428" t="n">
+        <v>2</v>
+      </c>
+      <c r="C428" t="n">
+        <v>1</v>
+      </c>
+      <c r="D428" t="inlineStr">
+        <is>
+          <t>5-a-side</t>
+        </is>
+      </c>
+      <c r="E428" t="inlineStr">
+        <is>
+          <t>Cerro</t>
+        </is>
+      </c>
+      <c r="F428" t="inlineStr">
+        <is>
+          <t>Outfield</t>
+        </is>
+      </c>
+      <c r="G428" t="inlineStr">
+        <is>
+          <t>Team B</t>
+        </is>
+      </c>
+      <c r="H428" t="inlineStr">
+        <is>
+          <t>Team A</t>
+        </is>
+      </c>
+      <c r="I428" t="inlineStr">
+        <is>
+          <t>Loss</t>
+        </is>
+      </c>
+      <c r="J428" t="n">
+        <v>9</v>
+      </c>
+      <c r="K428" t="n">
+        <v>3</v>
+      </c>
+      <c r="L428" t="n">
+        <v>0</v>
+      </c>
+      <c r="M428" t="n">
+        <v>0</v>
+      </c>
+      <c r="N428" t="n">
+        <v>0</v>
+      </c>
+      <c r="O428" t="n">
+        <v>0</v>
+      </c>
+      <c r="P428" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q428" t="n">
+        <v>10</v>
+      </c>
+      <c r="R428" t="n">
+        <v>5</v>
+      </c>
+      <c r="S428" t="n">
+        <v>10</v>
+      </c>
+      <c r="T428" t="n">
+        <v>-5</v>
+      </c>
+      <c r="U428" t="n">
+        <v>4</v>
+      </c>
+      <c r="V428" t="n">
+        <v>0</v>
+      </c>
+      <c r="W428" t="n">
+        <v>0</v>
+      </c>
+      <c r="X428" t="n">
+        <v>3</v>
+      </c>
+      <c r="Y428" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z428" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA428" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB428" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC428" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD428" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE428" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF428" t="n">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="429">
+      <c r="A429" s="2" t="n">
+        <v>45170</v>
+      </c>
+      <c r="B429" t="n">
+        <v>2</v>
+      </c>
+      <c r="C429" t="n">
+        <v>1</v>
+      </c>
+      <c r="D429" t="inlineStr">
+        <is>
+          <t>5-a-side</t>
+        </is>
+      </c>
+      <c r="E429" t="inlineStr">
+        <is>
+          <t>Mazzu</t>
+        </is>
+      </c>
+      <c r="F429" t="inlineStr">
+        <is>
+          <t>Outfield</t>
+        </is>
+      </c>
+      <c r="G429" t="inlineStr">
+        <is>
+          <t>Team B</t>
+        </is>
+      </c>
+      <c r="H429" t="inlineStr">
+        <is>
+          <t>Team A</t>
+        </is>
+      </c>
+      <c r="I429" t="inlineStr">
+        <is>
+          <t>Loss</t>
+        </is>
+      </c>
+      <c r="J429" t="n">
+        <v>9</v>
+      </c>
+      <c r="K429" t="n">
+        <v>2</v>
+      </c>
+      <c r="L429" t="n">
+        <v>0</v>
+      </c>
+      <c r="M429" t="n">
+        <v>0</v>
+      </c>
+      <c r="N429" t="n">
+        <v>0</v>
+      </c>
+      <c r="O429" t="n">
+        <v>0</v>
+      </c>
+      <c r="P429" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q429" t="n">
+        <v>10</v>
+      </c>
+      <c r="R429" t="n">
+        <v>5</v>
+      </c>
+      <c r="S429" t="n">
+        <v>10</v>
+      </c>
+      <c r="T429" t="n">
+        <v>-5</v>
+      </c>
+      <c r="U429" t="n">
+        <v>4</v>
+      </c>
+      <c r="V429" t="n">
+        <v>0</v>
+      </c>
+      <c r="W429" t="n">
+        <v>0</v>
+      </c>
+      <c r="X429" t="n">
+        <v>2</v>
+      </c>
+      <c r="Y429" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z429" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA429" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB429" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC429" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD429" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE429" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF429" t="n">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="430">
+      <c r="A430" s="2" t="n">
+        <v>45170</v>
+      </c>
+      <c r="B430" t="n">
+        <v>2</v>
+      </c>
+      <c r="C430" t="n">
+        <v>1</v>
+      </c>
+      <c r="D430" t="inlineStr">
+        <is>
+          <t>5-a-side</t>
+        </is>
+      </c>
+      <c r="E430" t="inlineStr">
+        <is>
+          <t>Davide Ang</t>
+        </is>
+      </c>
+      <c r="F430" t="inlineStr">
+        <is>
+          <t>Outfield</t>
+        </is>
+      </c>
+      <c r="G430" t="inlineStr">
+        <is>
+          <t>Team B</t>
+        </is>
+      </c>
+      <c r="H430" t="inlineStr">
+        <is>
+          <t>Team A</t>
+        </is>
+      </c>
+      <c r="I430" t="inlineStr">
+        <is>
+          <t>Loss</t>
+        </is>
+      </c>
+      <c r="J430" t="n">
+        <v>9</v>
+      </c>
+      <c r="K430" t="n">
+        <v>0</v>
+      </c>
+      <c r="L430" t="n">
+        <v>0</v>
+      </c>
+      <c r="M430" t="n">
+        <v>0</v>
+      </c>
+      <c r="N430" t="n">
+        <v>0</v>
+      </c>
+      <c r="O430" t="n">
+        <v>0</v>
+      </c>
+      <c r="P430" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q430" t="n">
+        <v>10</v>
+      </c>
+      <c r="R430" t="n">
+        <v>5</v>
+      </c>
+      <c r="S430" t="n">
+        <v>10</v>
+      </c>
+      <c r="T430" t="n">
+        <v>-5</v>
+      </c>
+      <c r="U430" t="n">
+        <v>4</v>
+      </c>
+      <c r="V430" t="n">
+        <v>0</v>
+      </c>
+      <c r="W430" t="n">
+        <v>0</v>
+      </c>
+      <c r="X430" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y430" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z430" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA430" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB430" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC430" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD430" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE430" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF430" t="n">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="431">
+      <c r="A431" s="2" t="n">
+        <v>45170</v>
+      </c>
+      <c r="B431" t="n">
+        <v>2</v>
+      </c>
+      <c r="C431" t="n">
+        <v>1</v>
+      </c>
+      <c r="D431" t="inlineStr">
+        <is>
+          <t>5-a-side</t>
+        </is>
+      </c>
+      <c r="E431" t="inlineStr">
+        <is>
+          <t>Andrea Scalambra</t>
+        </is>
+      </c>
+      <c r="F431" t="inlineStr">
+        <is>
+          <t>Outfield</t>
+        </is>
+      </c>
+      <c r="G431" t="inlineStr">
+        <is>
+          <t>Team B</t>
+        </is>
+      </c>
+      <c r="H431" t="inlineStr">
+        <is>
+          <t>Team A</t>
+        </is>
+      </c>
+      <c r="I431" t="inlineStr">
+        <is>
+          <t>Loss</t>
+        </is>
+      </c>
+      <c r="J431" t="n">
+        <v>9</v>
+      </c>
+      <c r="K431" t="n">
+        <v>0</v>
+      </c>
+      <c r="L431" t="n">
+        <v>0</v>
+      </c>
+      <c r="M431" t="n">
+        <v>0</v>
+      </c>
+      <c r="N431" t="n">
+        <v>0</v>
+      </c>
+      <c r="O431" t="n">
+        <v>0</v>
+      </c>
+      <c r="P431" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q431" t="n">
+        <v>10</v>
+      </c>
+      <c r="R431" t="n">
+        <v>5</v>
+      </c>
+      <c r="S431" t="n">
+        <v>10</v>
+      </c>
+      <c r="T431" t="n">
+        <v>-5</v>
+      </c>
+      <c r="U431" t="n">
+        <v>4</v>
+      </c>
+      <c r="V431" t="n">
+        <v>0</v>
+      </c>
+      <c r="W431" t="n">
+        <v>0</v>
+      </c>
+      <c r="X431" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y431" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z431" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA431" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB431" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC431" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD431" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE431" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF431" t="n">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="432">
+      <c r="A432" s="2" t="n">
+        <v>45179</v>
+      </c>
+      <c r="B432" t="n">
+        <v>2</v>
+      </c>
+      <c r="C432" t="n">
+        <v>2</v>
+      </c>
+      <c r="D432" t="inlineStr">
+        <is>
+          <t>5-a-side</t>
+        </is>
+      </c>
+      <c r="E432" t="inlineStr">
+        <is>
+          <t>Wissam Rahal</t>
+        </is>
+      </c>
+      <c r="F432" t="inlineStr">
+        <is>
+          <t>Offensive</t>
+        </is>
+      </c>
+      <c r="G432" t="inlineStr">
+        <is>
+          <t>Team A</t>
+        </is>
+      </c>
+      <c r="H432" t="inlineStr">
+        <is>
+          <t>Team B</t>
+        </is>
+      </c>
+      <c r="I432" t="inlineStr">
+        <is>
+          <t>Loss</t>
+        </is>
+      </c>
+      <c r="J432" t="n">
+        <v>9</v>
+      </c>
+      <c r="K432" t="n">
+        <v>0</v>
+      </c>
+      <c r="L432" t="n">
+        <v>0</v>
+      </c>
+      <c r="M432" t="n">
+        <v>0</v>
+      </c>
+      <c r="N432" t="n">
+        <v>0</v>
+      </c>
+      <c r="O432" t="n">
+        <v>0</v>
+      </c>
+      <c r="P432" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q432" t="n">
+        <v>2</v>
+      </c>
+      <c r="R432" t="n">
+        <v>6</v>
+      </c>
+      <c r="S432" t="n">
+        <v>6</v>
+      </c>
+      <c r="T432" t="n">
+        <v>-4</v>
+      </c>
+      <c r="U432" t="n">
+        <v>4</v>
+      </c>
+      <c r="V432" t="n">
+        <v>0</v>
+      </c>
+      <c r="W432" t="n">
+        <v>0</v>
+      </c>
+      <c r="X432" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y432" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z432" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA432" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB432" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC432" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD432" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE432" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF432" t="n">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="433">
+      <c r="A433" s="2" t="n">
+        <v>45179</v>
+      </c>
+      <c r="B433" t="n">
+        <v>2</v>
+      </c>
+      <c r="C433" t="n">
+        <v>2</v>
+      </c>
+      <c r="D433" t="inlineStr">
+        <is>
+          <t>5-a-side</t>
+        </is>
+      </c>
+      <c r="E433" t="inlineStr">
+        <is>
+          <t>Cameron McAinsh</t>
+        </is>
+      </c>
+      <c r="F433" t="inlineStr">
+        <is>
+          <t>Outfield</t>
+        </is>
+      </c>
+      <c r="G433" t="inlineStr">
+        <is>
+          <t>Team A</t>
+        </is>
+      </c>
+      <c r="H433" t="inlineStr">
+        <is>
+          <t>Team B</t>
+        </is>
+      </c>
+      <c r="I433" t="inlineStr">
+        <is>
+          <t>Loss</t>
+        </is>
+      </c>
+      <c r="J433" t="n">
+        <v>9</v>
+      </c>
+      <c r="K433" t="n">
+        <v>3</v>
+      </c>
+      <c r="L433" t="n">
+        <v>0</v>
+      </c>
+      <c r="M433" t="n">
+        <v>0</v>
+      </c>
+      <c r="N433" t="n">
+        <v>0</v>
+      </c>
+      <c r="O433" t="n">
+        <v>0</v>
+      </c>
+      <c r="P433" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q433" t="n">
+        <v>2</v>
+      </c>
+      <c r="R433" t="n">
+        <v>6</v>
+      </c>
+      <c r="S433" t="n">
+        <v>6</v>
+      </c>
+      <c r="T433" t="n">
+        <v>-4</v>
+      </c>
+      <c r="U433" t="n">
+        <v>4</v>
+      </c>
+      <c r="V433" t="n">
+        <v>0</v>
+      </c>
+      <c r="W433" t="n">
+        <v>0</v>
+      </c>
+      <c r="X433" t="n">
+        <v>3</v>
+      </c>
+      <c r="Y433" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z433" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA433" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB433" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC433" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD433" t="n">
+        <v>2</v>
+      </c>
+      <c r="AE433" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF433" t="n">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="434">
+      <c r="A434" s="2" t="n">
+        <v>45179</v>
+      </c>
+      <c r="B434" t="n">
+        <v>2</v>
+      </c>
+      <c r="C434" t="n">
+        <v>2</v>
+      </c>
+      <c r="D434" t="inlineStr">
+        <is>
+          <t>5-a-side</t>
+        </is>
+      </c>
+      <c r="E434" t="inlineStr">
+        <is>
+          <t>Damiano Barbanera</t>
+        </is>
+      </c>
+      <c r="F434" t="inlineStr">
+        <is>
+          <t>Defensive</t>
+        </is>
+      </c>
+      <c r="G434" t="inlineStr">
+        <is>
+          <t>Team A</t>
+        </is>
+      </c>
+      <c r="H434" t="inlineStr">
+        <is>
+          <t>Team B</t>
+        </is>
+      </c>
+      <c r="I434" t="inlineStr">
+        <is>
+          <t>Loss</t>
+        </is>
+      </c>
+      <c r="J434" t="n">
+        <v>9</v>
+      </c>
+      <c r="K434" t="n">
+        <v>1</v>
+      </c>
+      <c r="L434" t="n">
+        <v>0</v>
+      </c>
+      <c r="M434" t="n">
+        <v>0</v>
+      </c>
+      <c r="N434" t="n">
+        <v>0</v>
+      </c>
+      <c r="O434" t="n">
+        <v>0</v>
+      </c>
+      <c r="P434" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q434" t="n">
+        <v>2</v>
+      </c>
+      <c r="R434" t="n">
+        <v>6</v>
+      </c>
+      <c r="S434" t="n">
+        <v>6</v>
+      </c>
+      <c r="T434" t="n">
+        <v>-4</v>
+      </c>
+      <c r="U434" t="n">
+        <v>4</v>
+      </c>
+      <c r="V434" t="n">
+        <v>0</v>
+      </c>
+      <c r="W434" t="n">
+        <v>0</v>
+      </c>
+      <c r="X434" t="n">
+        <v>1</v>
+      </c>
+      <c r="Y434" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z434" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA434" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB434" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC434" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD434" t="n">
+        <v>4</v>
+      </c>
+      <c r="AE434" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF434" t="n">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="435">
+      <c r="A435" s="2" t="n">
+        <v>45179</v>
+      </c>
+      <c r="B435" t="n">
+        <v>2</v>
+      </c>
+      <c r="C435" t="n">
+        <v>2</v>
+      </c>
+      <c r="D435" t="inlineStr">
+        <is>
+          <t>5-a-side</t>
+        </is>
+      </c>
+      <c r="E435" t="inlineStr">
+        <is>
+          <t>Ludovico Righi</t>
+        </is>
+      </c>
+      <c r="F435" t="inlineStr">
+        <is>
+          <t>Outfield</t>
+        </is>
+      </c>
+      <c r="G435" t="inlineStr">
+        <is>
+          <t>Team A</t>
+        </is>
+      </c>
+      <c r="H435" t="inlineStr">
+        <is>
+          <t>Team B</t>
+        </is>
+      </c>
+      <c r="I435" t="inlineStr">
+        <is>
+          <t>Loss</t>
+        </is>
+      </c>
+      <c r="J435" t="n">
+        <v>9</v>
+      </c>
+      <c r="K435" t="n">
+        <v>0</v>
+      </c>
+      <c r="L435" t="n">
+        <v>0</v>
+      </c>
+      <c r="M435" t="n">
+        <v>0</v>
+      </c>
+      <c r="N435" t="n">
+        <v>0</v>
+      </c>
+      <c r="O435" t="n">
+        <v>0</v>
+      </c>
+      <c r="P435" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q435" t="n">
+        <v>2</v>
+      </c>
+      <c r="R435" t="n">
+        <v>6</v>
+      </c>
+      <c r="S435" t="n">
+        <v>6</v>
+      </c>
+      <c r="T435" t="n">
+        <v>-4</v>
+      </c>
+      <c r="U435" t="n">
+        <v>4</v>
+      </c>
+      <c r="V435" t="n">
+        <v>0</v>
+      </c>
+      <c r="W435" t="n">
+        <v>0</v>
+      </c>
+      <c r="X435" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y435" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z435" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA435" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB435" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC435" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD435" t="n">
+        <v>2</v>
+      </c>
+      <c r="AE435" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF435" t="n">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="436">
+      <c r="A436" s="2" t="n">
+        <v>45179</v>
+      </c>
+      <c r="B436" t="n">
+        <v>2</v>
+      </c>
+      <c r="C436" t="n">
+        <v>2</v>
+      </c>
+      <c r="D436" t="inlineStr">
+        <is>
+          <t>5-a-side</t>
+        </is>
+      </c>
+      <c r="E436" t="inlineStr">
+        <is>
+          <t>Federico Paolucci</t>
+        </is>
+      </c>
+      <c r="F436" t="inlineStr">
+        <is>
+          <t>Outfield</t>
+        </is>
+      </c>
+      <c r="G436" t="inlineStr">
+        <is>
+          <t>Team B</t>
+        </is>
+      </c>
+      <c r="H436" t="inlineStr">
+        <is>
+          <t>Team B</t>
+        </is>
+      </c>
+      <c r="I436" t="inlineStr">
+        <is>
+          <t>Win</t>
+        </is>
+      </c>
+      <c r="J436" t="n">
+        <v>9</v>
+      </c>
+      <c r="K436" t="n">
+        <v>0</v>
+      </c>
+      <c r="L436" t="n">
+        <v>0</v>
+      </c>
+      <c r="M436" t="n">
+        <v>0</v>
+      </c>
+      <c r="N436" t="n">
+        <v>0</v>
+      </c>
+      <c r="O436" t="n">
+        <v>0</v>
+      </c>
+      <c r="P436" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q436" t="n">
+        <v>2</v>
+      </c>
+      <c r="R436" t="n">
+        <v>6</v>
+      </c>
+      <c r="S436" t="n">
+        <v>2</v>
+      </c>
+      <c r="T436" t="n">
+        <v>4</v>
+      </c>
+      <c r="U436" t="n">
+        <v>4</v>
+      </c>
+      <c r="V436" t="n">
+        <v>3</v>
+      </c>
+      <c r="W436" t="n">
+        <v>0</v>
+      </c>
+      <c r="X436" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y436" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z436" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA436" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB436" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC436" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD436" t="n">
+        <v>4</v>
+      </c>
+      <c r="AE436" t="n">
+        <v>4</v>
+      </c>
+      <c r="AF436" t="n">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="437">
+      <c r="A437" s="2" t="n">
+        <v>45179</v>
+      </c>
+      <c r="B437" t="n">
+        <v>2</v>
+      </c>
+      <c r="C437" t="n">
+        <v>2</v>
+      </c>
+      <c r="D437" t="inlineStr">
+        <is>
+          <t>5-a-side</t>
+        </is>
+      </c>
+      <c r="E437" t="inlineStr">
+        <is>
+          <t>Cerro</t>
+        </is>
+      </c>
+      <c r="F437" t="inlineStr">
+        <is>
+          <t>Outfield</t>
+        </is>
+      </c>
+      <c r="G437" t="inlineStr">
+        <is>
+          <t>Team B</t>
+        </is>
+      </c>
+      <c r="H437" t="inlineStr">
+        <is>
+          <t>Team B</t>
+        </is>
+      </c>
+      <c r="I437" t="inlineStr">
+        <is>
+          <t>Win</t>
+        </is>
+      </c>
+      <c r="J437" t="n">
+        <v>9</v>
+      </c>
+      <c r="K437" t="n">
+        <v>3</v>
+      </c>
+      <c r="L437" t="n">
+        <v>0</v>
+      </c>
+      <c r="M437" t="n">
+        <v>0</v>
+      </c>
+      <c r="N437" t="n">
+        <v>0</v>
+      </c>
+      <c r="O437" t="n">
+        <v>0</v>
+      </c>
+      <c r="P437" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q437" t="n">
+        <v>2</v>
+      </c>
+      <c r="R437" t="n">
+        <v>6</v>
+      </c>
+      <c r="S437" t="n">
+        <v>2</v>
+      </c>
+      <c r="T437" t="n">
+        <v>4</v>
+      </c>
+      <c r="U437" t="n">
+        <v>4</v>
+      </c>
+      <c r="V437" t="n">
+        <v>3</v>
+      </c>
+      <c r="W437" t="n">
+        <v>0</v>
+      </c>
+      <c r="X437" t="n">
+        <v>3</v>
+      </c>
+      <c r="Y437" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z437" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA437" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB437" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC437" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD437" t="n">
+        <v>4</v>
+      </c>
+      <c r="AE437" t="n">
+        <v>4</v>
+      </c>
+      <c r="AF437" t="n">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="438">
+      <c r="A438" s="2" t="n">
+        <v>45179</v>
+      </c>
+      <c r="B438" t="n">
+        <v>2</v>
+      </c>
+      <c r="C438" t="n">
+        <v>2</v>
+      </c>
+      <c r="D438" t="inlineStr">
+        <is>
+          <t>5-a-side</t>
+        </is>
+      </c>
+      <c r="E438" t="inlineStr">
+        <is>
+          <t>Mazzu</t>
+        </is>
+      </c>
+      <c r="F438" t="inlineStr">
+        <is>
+          <t>Outfield</t>
+        </is>
+      </c>
+      <c r="G438" t="inlineStr">
+        <is>
+          <t>Team B</t>
+        </is>
+      </c>
+      <c r="H438" t="inlineStr">
+        <is>
+          <t>Team B</t>
+        </is>
+      </c>
+      <c r="I438" t="inlineStr">
+        <is>
+          <t>Win</t>
+        </is>
+      </c>
+      <c r="J438" t="n">
+        <v>9</v>
+      </c>
+      <c r="K438" t="n">
+        <v>2</v>
+      </c>
+      <c r="L438" t="n">
+        <v>0</v>
+      </c>
+      <c r="M438" t="n">
+        <v>0</v>
+      </c>
+      <c r="N438" t="n">
+        <v>0</v>
+      </c>
+      <c r="O438" t="n">
+        <v>0</v>
+      </c>
+      <c r="P438" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q438" t="n">
+        <v>2</v>
+      </c>
+      <c r="R438" t="n">
+        <v>6</v>
+      </c>
+      <c r="S438" t="n">
+        <v>2</v>
+      </c>
+      <c r="T438" t="n">
+        <v>4</v>
+      </c>
+      <c r="U438" t="n">
+        <v>4</v>
+      </c>
+      <c r="V438" t="n">
+        <v>3</v>
+      </c>
+      <c r="W438" t="n">
+        <v>0</v>
+      </c>
+      <c r="X438" t="n">
+        <v>2</v>
+      </c>
+      <c r="Y438" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z438" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA438" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB438" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC438" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD438" t="n">
+        <v>4</v>
+      </c>
+      <c r="AE438" t="n">
+        <v>4</v>
+      </c>
+      <c r="AF438" t="n">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="439">
+      <c r="A439" s="2" t="n">
+        <v>45179</v>
+      </c>
+      <c r="B439" t="n">
+        <v>2</v>
+      </c>
+      <c r="C439" t="n">
+        <v>2</v>
+      </c>
+      <c r="D439" t="inlineStr">
+        <is>
+          <t>5-a-side</t>
+        </is>
+      </c>
+      <c r="E439" t="inlineStr">
+        <is>
+          <t>Davide Ang</t>
+        </is>
+      </c>
+      <c r="F439" t="inlineStr">
+        <is>
+          <t>Outfield</t>
+        </is>
+      </c>
+      <c r="G439" t="inlineStr">
+        <is>
+          <t>Team B</t>
+        </is>
+      </c>
+      <c r="H439" t="inlineStr">
+        <is>
+          <t>Team B</t>
+        </is>
+      </c>
+      <c r="I439" t="inlineStr">
+        <is>
+          <t>Win</t>
+        </is>
+      </c>
+      <c r="J439" t="n">
+        <v>9</v>
+      </c>
+      <c r="K439" t="n">
+        <v>0</v>
+      </c>
+      <c r="L439" t="n">
+        <v>0</v>
+      </c>
+      <c r="M439" t="n">
+        <v>0</v>
+      </c>
+      <c r="N439" t="n">
+        <v>0</v>
+      </c>
+      <c r="O439" t="n">
+        <v>0</v>
+      </c>
+      <c r="P439" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q439" t="n">
+        <v>2</v>
+      </c>
+      <c r="R439" t="n">
+        <v>6</v>
+      </c>
+      <c r="S439" t="n">
+        <v>2</v>
+      </c>
+      <c r="T439" t="n">
+        <v>4</v>
+      </c>
+      <c r="U439" t="n">
+        <v>4</v>
+      </c>
+      <c r="V439" t="n">
+        <v>3</v>
+      </c>
+      <c r="W439" t="n">
+        <v>0</v>
+      </c>
+      <c r="X439" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y439" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z439" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA439" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB439" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC439" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD439" t="n">
+        <v>4</v>
+      </c>
+      <c r="AE439" t="n">
+        <v>4</v>
+      </c>
+      <c r="AF439" t="n">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="440">
+      <c r="A440" s="2" t="n">
+        <v>45179</v>
+      </c>
+      <c r="B440" t="n">
+        <v>2</v>
+      </c>
+      <c r="C440" t="n">
+        <v>2</v>
+      </c>
+      <c r="D440" t="inlineStr">
+        <is>
+          <t>5-a-side</t>
+        </is>
+      </c>
+      <c r="E440" t="inlineStr">
+        <is>
+          <t>Andrea Scalambra</t>
+        </is>
+      </c>
+      <c r="F440" t="inlineStr">
+        <is>
+          <t>Outfield</t>
+        </is>
+      </c>
+      <c r="G440" t="inlineStr">
+        <is>
+          <t>Team B</t>
+        </is>
+      </c>
+      <c r="H440" t="inlineStr">
+        <is>
+          <t>Team B</t>
+        </is>
+      </c>
+      <c r="I440" t="inlineStr">
+        <is>
+          <t>Win</t>
+        </is>
+      </c>
+      <c r="J440" t="n">
+        <v>9</v>
+      </c>
+      <c r="K440" t="n">
+        <v>0</v>
+      </c>
+      <c r="L440" t="n">
+        <v>0</v>
+      </c>
+      <c r="M440" t="n">
+        <v>0</v>
+      </c>
+      <c r="N440" t="n">
+        <v>0</v>
+      </c>
+      <c r="O440" t="n">
+        <v>0</v>
+      </c>
+      <c r="P440" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q440" t="n">
+        <v>2</v>
+      </c>
+      <c r="R440" t="n">
+        <v>6</v>
+      </c>
+      <c r="S440" t="n">
+        <v>2</v>
+      </c>
+      <c r="T440" t="n">
+        <v>4</v>
+      </c>
+      <c r="U440" t="n">
+        <v>4</v>
+      </c>
+      <c r="V440" t="n">
+        <v>3</v>
+      </c>
+      <c r="W440" t="n">
+        <v>0</v>
+      </c>
+      <c r="X440" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y440" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z440" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA440" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB440" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC440" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD440" t="n">
+        <v>4</v>
+      </c>
+      <c r="AE440" t="n">
+        <v>4</v>
+      </c>
+      <c r="AF440" t="n">
+        <v>15</v>
       </c>
     </row>
   </sheetData>

--- a/Middleput/points.xlsx
+++ b/Middleput/points.xlsx
@@ -13921,7 +13921,7 @@
       </c>
       <c r="E123" t="inlineStr">
         <is>
-          <t>Daniele (Francesco)</t>
+          <t>Daniele Miccoli</t>
         </is>
       </c>
       <c r="F123" t="inlineStr">
@@ -14361,7 +14361,7 @@
       </c>
       <c r="E127" t="inlineStr">
         <is>
-          <t>Daniele (Francesco)</t>
+          <t>Daniele Miccoli</t>
         </is>
       </c>
       <c r="F127" t="inlineStr">
@@ -18431,7 +18431,7 @@
       </c>
       <c r="E164" t="inlineStr">
         <is>
-          <t>Daniele (Francesco)</t>
+          <t>Daniele Miccoli</t>
         </is>
       </c>
       <c r="F164" t="inlineStr">
@@ -21621,7 +21621,7 @@
       </c>
       <c r="E193" t="inlineStr">
         <is>
-          <t>Daniele (Francesco)</t>
+          <t>Daniele Miccoli</t>
         </is>
       </c>
       <c r="F193" t="inlineStr">
@@ -24371,7 +24371,7 @@
       </c>
       <c r="E218" t="inlineStr">
         <is>
-          <t>Daniele (Francesco)</t>
+          <t>Daniele Miccoli</t>
         </is>
       </c>
       <c r="F218" t="inlineStr">
@@ -26021,7 +26021,7 @@
       </c>
       <c r="E233" t="inlineStr">
         <is>
-          <t>Daniele (Francesco)</t>
+          <t>Daniele Miccoli</t>
         </is>
       </c>
       <c r="F233" t="inlineStr">
@@ -26681,7 +26681,7 @@
       </c>
       <c r="E239" t="inlineStr">
         <is>
-          <t>Daniele (Francesco)</t>
+          <t>Daniele Miccoli</t>
         </is>
       </c>
       <c r="F239" t="inlineStr">
@@ -28881,7 +28881,7 @@
       </c>
       <c r="E259" t="inlineStr">
         <is>
-          <t>Daniele (Francesco)</t>
+          <t>Daniele Miccoli</t>
         </is>
       </c>
       <c r="F259" t="inlineStr">
@@ -30531,7 +30531,7 @@
       </c>
       <c r="E274" t="inlineStr">
         <is>
-          <t>Daniele (Francesco)</t>
+          <t>Daniele Miccoli</t>
         </is>
       </c>
       <c r="F274" t="inlineStr">
@@ -31961,7 +31961,7 @@
       </c>
       <c r="E287" t="inlineStr">
         <is>
-          <t>Daniele (Francesco)</t>
+          <t>Daniele Miccoli</t>
         </is>
       </c>
       <c r="F287" t="inlineStr">
@@ -33171,7 +33171,7 @@
       </c>
       <c r="E298" t="inlineStr">
         <is>
-          <t>Daniele (Francesco)</t>
+          <t>Daniele Miccoli</t>
         </is>
       </c>
       <c r="F298" t="inlineStr">
@@ -34491,7 +34491,7 @@
       </c>
       <c r="E310" t="inlineStr">
         <is>
-          <t>Daniele (Francesco)</t>
+          <t>Daniele Miccoli</t>
         </is>
       </c>
       <c r="F310" t="inlineStr">
@@ -37021,7 +37021,7 @@
       </c>
       <c r="E333" t="inlineStr">
         <is>
-          <t>Daniele (Francesco)</t>
+          <t>Daniele Miccoli</t>
         </is>
       </c>
       <c r="F333" t="inlineStr">
@@ -38451,7 +38451,7 @@
       </c>
       <c r="E346" t="inlineStr">
         <is>
-          <t>Daniele (Francesco)</t>
+          <t>Daniele Miccoli</t>
         </is>
       </c>
       <c r="F346" t="inlineStr">
@@ -41311,7 +41311,7 @@
       </c>
       <c r="E372" t="inlineStr">
         <is>
-          <t>Daniele (Francesco)</t>
+          <t>Daniele Miccoli</t>
         </is>
       </c>
       <c r="F372" t="inlineStr">
@@ -42411,7 +42411,7 @@
       </c>
       <c r="E382" t="inlineStr">
         <is>
-          <t>Daniele (Francesco)</t>
+          <t>Daniele Miccoli</t>
         </is>
       </c>
       <c r="F382" t="inlineStr">
@@ -44721,7 +44721,7 @@
       </c>
       <c r="E403" t="inlineStr">
         <is>
-          <t>Daniele (Francesco)</t>
+          <t>Daniele Miccoli</t>
         </is>
       </c>
       <c r="F403" t="inlineStr">

--- a/Middleput/points.xlsx
+++ b/Middleput/points.xlsx
@@ -46963,7 +46963,7 @@
       </c>
       <c r="Q423" t="inlineStr">
         <is>
-          <t>Offensive</t>
+          <t>Outfield</t>
         </is>
       </c>
       <c r="R423" t="n">
@@ -47002,7 +47002,7 @@
         <v>5</v>
       </c>
       <c r="AC423" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="AD423" t="n">
         <v>5</v>
@@ -47011,7 +47011,7 @@
         <v>3</v>
       </c>
       <c r="AF423" t="n">
-        <v>12</v>
+        <v>15</v>
       </c>
     </row>
     <row r="424">
@@ -47953,7 +47953,7 @@
       </c>
       <c r="Q432" t="inlineStr">
         <is>
-          <t>Offensive</t>
+          <t>Outfield</t>
         </is>
       </c>
       <c r="R432" t="n">
@@ -47992,7 +47992,7 @@
         <v>6</v>
       </c>
       <c r="AC432" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AD432" t="n">
         <v>0</v>
@@ -48001,7 +48001,7 @@
         <v>0</v>
       </c>
       <c r="AF432" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
     </row>
     <row r="433">
@@ -48173,7 +48173,7 @@
       </c>
       <c r="Q434" t="inlineStr">
         <is>
-          <t>Defensive</t>
+          <t>Outfield</t>
         </is>
       </c>
       <c r="R434" t="n">
@@ -48212,7 +48212,7 @@
         <v>6</v>
       </c>
       <c r="AC434" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="AD434" t="n">
         <v>0</v>
@@ -48221,7 +48221,7 @@
         <v>0</v>
       </c>
       <c r="AF434" t="n">
-        <v>9</v>
+        <v>7</v>
       </c>
     </row>
     <row r="435">
